--- a/thesis/foundationalDataset/non_covered_concepts.xlsx
+++ b/thesis/foundationalDataset/non_covered_concepts.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/Master Thesis Dataset/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/thesis/foundationalDataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3830E13B-AF2E-BE44-A0FC-000AD32A48E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6499A8CA-C195-8941-A4E9-411093430D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14760" yWindow="900" windowWidth="14480" windowHeight="16580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -314,7 +314,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -323,22 +323,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="12"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -353,7 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="-0.499984740745262"/>
+        <fgColor rgb="FF3E552A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -370,20 +379,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF3E552A"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -681,20 +696,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.83203125" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:3" s="5" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -705,7 +726,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -716,7 +737,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -727,7 +748,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
@@ -738,7 +759,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -749,7 +770,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -760,7 +781,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -771,7 +792,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
@@ -782,7 +803,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -793,7 +814,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
@@ -804,7 +825,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -815,7 +836,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
@@ -826,7 +847,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>5</v>
       </c>
@@ -837,7 +858,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>5</v>
       </c>
@@ -848,7 +869,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>5</v>
       </c>
@@ -859,18 +880,18 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>9</v>
       </c>
@@ -881,7 +902,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
@@ -892,7 +913,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
@@ -903,7 +924,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
@@ -914,7 +935,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
@@ -925,7 +946,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
@@ -936,7 +957,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>9</v>
       </c>
@@ -947,7 +968,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>9</v>
       </c>
@@ -958,7 +979,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>12</v>
       </c>
@@ -969,7 +990,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>12</v>
       </c>
@@ -980,7 +1001,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>12</v>
       </c>
@@ -991,7 +1012,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>12</v>
       </c>
@@ -1002,7 +1023,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>12</v>
       </c>
@@ -1013,7 +1034,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>13</v>
       </c>
@@ -1024,7 +1045,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>13</v>
       </c>
@@ -1035,7 +1056,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>13</v>
       </c>
@@ -1046,7 +1067,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>13</v>
       </c>
@@ -1057,7 +1078,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>13</v>
       </c>
@@ -1068,7 +1089,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>13</v>
       </c>
@@ -1079,7 +1100,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>13</v>
       </c>
@@ -1090,7 +1111,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>13</v>
       </c>
@@ -1101,7 +1122,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>13</v>
       </c>
@@ -1112,7 +1133,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>13</v>
       </c>
@@ -1123,7 +1144,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>13</v>
       </c>
@@ -1134,7 +1155,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>13</v>
       </c>
@@ -1145,7 +1166,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>13</v>
       </c>
@@ -1156,7 +1177,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>13</v>
       </c>
@@ -1167,7 +1188,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>13</v>
       </c>
@@ -1178,7 +1199,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>13</v>
       </c>
@@ -1189,7 +1210,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>14</v>
       </c>
@@ -1200,7 +1221,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>14</v>
       </c>
@@ -1211,7 +1232,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>14</v>
       </c>
@@ -1222,7 +1243,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>14</v>
       </c>
@@ -1233,7 +1254,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>14</v>
       </c>
@@ -1244,7 +1265,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>14</v>
       </c>
@@ -1255,7 +1276,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>14</v>
       </c>
@@ -1266,7 +1287,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>14</v>
       </c>
